--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE48"/>
+  <dimension ref="A1:AE49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 889-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46075</v>
+        <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -992,58 +992,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46080</v>
+        <v>46075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,34 +1073,34 @@
         </is>
       </c>
       <c r="I6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="n">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1113,42 +1113,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1165,7 +1165,7 @@
         <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,13 +1178,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1218,42 +1218,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 889-2026</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46029</v>
+        <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1316,42 +1316,42 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1473,14 +1473,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44937</v>
+        <v>45791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44912</v>
+        <v>46036</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44896</v>
+        <v>46036</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45666</v>
+        <v>45905</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 34394-2025</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45846</v>
+        <v>45666</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32577-2025</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45838</v>
+        <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45063</v>
+        <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45847</v>
+        <v>45919</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45905</v>
+        <v>45847</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2120,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 34394-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46075</v>
+        <v>45846</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2193,7 +2193,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 32577-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45919</v>
+        <v>45838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45919</v>
+        <v>45303</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2295,8 +2295,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2339,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2353,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45919</v>
+        <v>46075</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2369,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2412,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2426,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44973</v>
+        <v>46079</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2442,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.7</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2502,7 +2507,7 @@
         <v>46079</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2558,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2572,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46079</v>
+        <v>46126</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2588,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2631,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2645,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45303</v>
+        <v>45977</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2660,13 +2665,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45977</v>
+        <v>45981</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45981</v>
+        <v>44912</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46126</v>
+        <v>45063</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44973</v>
+        <v>46154</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.1</v>
+        <v>7.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46036</v>
+        <v>46246</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46036</v>
+        <v>46251</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>7.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46154</v>
+        <v>46253</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45260</v>
+        <v>44973</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>5.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45631</v>
+        <v>45791</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46246</v>
+        <v>45062</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46251</v>
+        <v>44910</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.7</v>
+        <v>4.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46253</v>
+        <v>44912</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44896</v>
+        <v>46275</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44912</v>
+        <v>46275</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45062</v>
+        <v>46279</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45791</v>
+        <v>45987</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44910</v>
+        <v>44896</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46275</v>
+        <v>44973</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4033,14 +4033,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45987</v>
+        <v>44937</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46275</v>
+        <v>45260</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,134 +4183,207 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>TJÖRN</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A 57955-2024</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>45631</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>TJÖRN</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>A 23294-2025</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="n">
         <v>45791</v>
       </c>
-      <c r="E47" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>TJÖRN</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>A 23294-2025</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>45791</v>
-      </c>
-      <c r="E48" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>TJÖRN</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
+      <c r="E49" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>TJÖRN</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
         <v>4.6</v>
       </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="2" t="inlineStr"/>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 889-2026</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46029</v>
+        <v>46080</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -1001,49 +1001,49 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46075</v>
+        <v>46080</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,19 +1073,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1097,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1113,42 +1113,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 889-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46080</v>
+        <v>46029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1211,49 +1211,49 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46080</v>
+        <v>46075</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,20 +1283,20 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -1307,10 +1307,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1323,35 +1323,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1473,14 +1473,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45791</v>
+        <v>44937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46036</v>
+        <v>45260</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46036</v>
+        <v>46079</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45905</v>
+        <v>46079</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45666</v>
+        <v>45631</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45919</v>
+        <v>45905</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45919</v>
+        <v>44912</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45919</v>
+        <v>44896</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>7.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45847</v>
+        <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2120,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 34394-2025</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45846</v>
+        <v>45919</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2193,7 +2193,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32577-2025</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45838</v>
+        <v>45919</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45303</v>
+        <v>46126</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2295,13 +2295,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2339,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2353,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46075</v>
+        <v>45303</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2373,8 +2368,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46079</v>
+        <v>45063</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46079</v>
+        <v>44973</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46126</v>
+        <v>45977</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45977</v>
+        <v>45981</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45981</v>
+        <v>46154</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>7.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44912</v>
+        <v>46036</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45063</v>
+        <v>46036</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.8</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46154</v>
+        <v>44973</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>7.3</v>
+        <v>3.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46246</v>
+        <v>46075</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46251</v>
+        <v>44896</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7.7</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46253</v>
+        <v>44912</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44973</v>
+        <v>46246</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45791</v>
+        <v>46251</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>7.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45062</v>
+        <v>46253</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44910</v>
+        <v>45062</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44912</v>
+        <v>45791</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46275</v>
+        <v>44910</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>46275</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46279</v>
+        <v>45987</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45987</v>
+        <v>46275</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44896</v>
+        <v>46279</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44973</v>
+        <v>45791</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4033,14 +4033,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44937</v>
+        <v>45791</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.2</v>
+        <v>4.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45260</v>
+        <v>45666</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 34394-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44896</v>
+        <v>45846</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.5</v>
+        <v>3.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 32577-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45631</v>
+        <v>45838</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45791</v>
+        <v>45847</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE49"/>
+  <dimension ref="A1:AE50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 889-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46080</v>
+        <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -1001,49 +1001,49 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 34591-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46080</v>
+        <v>44795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,20 +1073,20 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
@@ -1097,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1113,42 +1113,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blågrönt mannagräs</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 889-2026</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46029</v>
+        <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,20 +1178,20 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
@@ -1202,58 +1202,58 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46075</v>
+        <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1295,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1307,10 +1307,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1323,42 +1323,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 34591-2022</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44795</v>
+        <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,19 +1388,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1428,42 +1428,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Blågrönt mannagräs</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1473,14 +1473,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44937</v>
+        <v>45666</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45260</v>
+        <v>45905</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46079</v>
+        <v>46036</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46079</v>
+        <v>45919</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45631</v>
+        <v>45919</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45905</v>
+        <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44912</v>
+        <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 34394-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44896</v>
+        <v>45846</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>7.5</v>
+        <v>3.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 32577-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45919</v>
+        <v>45838</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2120,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45919</v>
+        <v>46036</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2193,7 +2193,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45919</v>
+        <v>45303</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2222,8 +2222,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2266,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2280,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46126</v>
+        <v>45977</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2296,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2339,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2353,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45303</v>
+        <v>45981</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2368,13 +2373,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45063</v>
+        <v>46075</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44973</v>
+        <v>46079</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.7</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45977</v>
+        <v>46079</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45981</v>
+        <v>44912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46154</v>
+        <v>45063</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.3</v>
+        <v>5.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46036</v>
+        <v>46126</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46036</v>
+        <v>44973</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44973</v>
+        <v>44912</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46075</v>
+        <v>46154</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>7.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>44896</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44912</v>
+        <v>44973</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3230,14 +3230,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46246</v>
+        <v>44937</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46251</v>
+        <v>45260</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46253</v>
+        <v>44896</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>7.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45062</v>
+        <v>46246</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45791</v>
+        <v>46251</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>7.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44910</v>
+        <v>46253</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46275</v>
+        <v>45631</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45987</v>
+        <v>45791</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46275</v>
+        <v>45062</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46279</v>
+        <v>44910</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45791</v>
+        <v>46275</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45791</v>
+        <v>46275</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45666</v>
+        <v>46279</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 34394-2025</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45846</v>
+        <v>45987</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 32577-2025</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45838</v>
+        <v>46280</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4312,10 +4312,10 @@
       </c>
       <c r="V48" s="2" t="inlineStr"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45847</v>
+        <v>45791</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4384,6 +4384,79 @@
         <v>0</v>
       </c>
       <c r="V49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>A 23301-2025</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>45791</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>TJÖRN</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 889-2026</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46029</v>
+        <v>46075</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -968,20 +968,20 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
@@ -992,58 +992,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 34591-2022</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44795</v>
+        <v>46080</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1097,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1113,42 +1113,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Blågrönt mannagräs</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46075</v>
+        <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1202,10 +1202,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1218,42 +1218,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 34591-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46080</v>
+        <v>44795</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,34 +1283,34 @@
         </is>
       </c>
       <c r="I8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="J8" t="n">
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1323,42 +1323,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blågrönt mannagräs</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 889-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46080</v>
+        <v>46029</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,13 +1388,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1421,49 +1421,49 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1473,14 +1473,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45666</v>
+        <v>44937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45905</v>
+        <v>44912</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46036</v>
+        <v>44896</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45919</v>
+        <v>45666</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45919</v>
+        <v>46075</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45919</v>
+        <v>46079</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45847</v>
+        <v>46079</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 34394-2025</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45846</v>
+        <v>45063</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32577-2025</t>
+          <t>A 34394-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45838</v>
+        <v>45846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2120,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 32577-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46036</v>
+        <v>45838</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2193,7 +2193,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45303</v>
+        <v>45847</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2222,13 +2222,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2266,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2280,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45977</v>
+        <v>44973</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2296,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>5.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2339,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2353,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45981</v>
+        <v>46126</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2369,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2412,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2426,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46075</v>
+        <v>45905</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2442,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2485,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2499,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46079</v>
+        <v>45919</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2515,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2558,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2572,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46079</v>
+        <v>45919</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2588,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2631,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2645,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44912</v>
+        <v>45919</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2661,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2704,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2718,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45063</v>
+        <v>45303</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2738,8 +2733,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46126</v>
+        <v>46154</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.7</v>
+        <v>7.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2872,7 +2872,7 @@
         <v>44973</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44912</v>
+        <v>45977</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46154</v>
+        <v>46246</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7.3</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44896</v>
+        <v>45981</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44973</v>
+        <v>46251</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>7.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3230,14 +3230,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44937</v>
+        <v>46253</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3310,7 +3310,7 @@
         <v>45260</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44896</v>
+        <v>45631</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7.5</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46246</v>
+        <v>45062</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46251</v>
+        <v>45791</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7.7</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46253</v>
+        <v>44910</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45631</v>
+        <v>46275</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45791</v>
+        <v>46275</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45062</v>
+        <v>46279</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44910</v>
+        <v>45987</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46275</v>
+        <v>46036</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46279</v>
+        <v>46036</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45987</v>
+        <v>44896</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46280</v>
+        <v>44912</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4332,7 +4332,7 @@
         <v>45791</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4405,7 +4405,7 @@
         <v>45791</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE50"/>
+  <dimension ref="A1:AE51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 34591-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46075</v>
+        <v>44795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1008,42 +1008,42 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Blågrönt mannagräs</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 889-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46080</v>
+        <v>46029</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1106,49 +1106,49 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46080</v>
+        <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,20 +1178,20 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
@@ -1202,10 +1202,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1218,42 +1218,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 34591-2022</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44795</v>
+        <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1295,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1307,10 +1307,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1323,42 +1323,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blågrönt mannagräs</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 889-2026</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46029</v>
+        <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,13 +1388,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1421,49 +1421,49 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1473,14 +1473,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44937</v>
+        <v>45905</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>44912</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44896</v>
+        <v>45919</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>7.5</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45666</v>
+        <v>45919</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46075</v>
+        <v>45919</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46079</v>
+        <v>45063</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46079</v>
+        <v>45303</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1930,8 +1930,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1979,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1993,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45063</v>
+        <v>44973</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2004,7 +2009,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2052,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 34394-2025</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2066,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45846</v>
+        <v>46154</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2082,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.9</v>
+        <v>7.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2125,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32577-2025</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2139,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45838</v>
+        <v>45977</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2150,7 +2155,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5.3</v>
+        <v>2.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2193,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2207,10 +2212,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45847</v>
+        <v>45981</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2223,7 +2228,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2266,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2280,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44973</v>
+        <v>44912</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2296,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2339,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2353,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46126</v>
+        <v>44896</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2369,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2412,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2426,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45905</v>
+        <v>46036</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2442,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2485,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2499,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45919</v>
+        <v>46036</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2515,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2558,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2572,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45919</v>
+        <v>44973</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2588,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2631,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2641,14 +2646,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45919</v>
+        <v>44937</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2661,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2704,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2718,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45303</v>
+        <v>45260</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2733,13 +2738,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46154</v>
+        <v>46075</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>7.3</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44973</v>
+        <v>44896</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.1</v>
+        <v>7.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45977</v>
+        <v>46079</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46246</v>
+        <v>46079</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45981</v>
+        <v>46126</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46251</v>
+        <v>46246</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.7</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>7.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45260</v>
+        <v>46253</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>45631</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45062</v>
+        <v>45791</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45791</v>
+        <v>45062</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3602,7 +3602,7 @@
         <v>44910</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3675,7 +3675,7 @@
         <v>46275</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3748,7 +3748,7 @@
         <v>46275</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         <v>46279</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45987</v>
+        <v>45791</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46280</v>
+        <v>45791</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46036</v>
+        <v>46280</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46036</v>
+        <v>45987</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44896</v>
+        <v>46283</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44912</v>
+        <v>45666</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45791</v>
+        <v>45847</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4385,10 +4385,10 @@
       </c>
       <c r="V49" s="2" t="inlineStr"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 34394-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45791</v>
+        <v>45846</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4457,6 +4457,79 @@
         <v>0</v>
       </c>
       <c r="V50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>A 32577-2025</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>45838</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>TJÖRN</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46029</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>45905</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>44912</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45919</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>45919</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45919</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45063</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>45303</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>44973</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46154</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>45977</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>45981</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>44912</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>44896</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>46036</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>46036</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>44973</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>44937</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45260</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>46075</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>44896</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>46079</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>46079</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>46126</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>46246</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46251</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>46253</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45631</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45791</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45062</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44910</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>46275</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>46275</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>46279</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>45791</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45791</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>46280</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>45987</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>46283</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45666</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45847</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>45846</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>45838</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46029</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>45905</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44912</v>
+        <v>45919</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1626,7 +1626,7 @@
         <v>45919</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1699,7 +1699,7 @@
         <v>45919</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45919</v>
+        <v>45303</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1784,8 +1784,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1833,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1847,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45063</v>
+        <v>44912</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1863,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1906,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1920,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45303</v>
+        <v>46154</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1930,13 +1935,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>7.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1993,10 +1993,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44973</v>
+        <v>45063</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46154</v>
+        <v>45977</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2125,7 +2125,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2139,10 +2139,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45977</v>
+        <v>45981</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45981</v>
+        <v>44973</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44912</v>
+        <v>46036</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44896</v>
+        <v>46036</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46036</v>
+        <v>44912</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46036</v>
+        <v>46075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44973</v>
+        <v>46079</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2646,14 +2646,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44937</v>
+        <v>46079</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45260</v>
+        <v>44896</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46075</v>
+        <v>44973</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44896</v>
+        <v>46246</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2938,14 +2938,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46079</v>
+        <v>44937</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46079</v>
+        <v>45260</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46126</v>
+        <v>46251</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.7</v>
+        <v>7.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46246</v>
+        <v>46126</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46251</v>
+        <v>44896</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3310,7 +3310,7 @@
         <v>46253</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45631</v>
+        <v>45791</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45791</v>
+        <v>45062</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45062</v>
+        <v>44910</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44910</v>
+        <v>46275</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3675,7 +3675,7 @@
         <v>46275</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45791</v>
+        <v>45987</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45791</v>
+        <v>46283</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46280</v>
+        <v>45631</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45987</v>
+        <v>45791</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46283</v>
+        <v>45791</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4259,7 +4259,7 @@
         <v>45666</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45847</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>45846</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>45838</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46029</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45905</v>
+        <v>45791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45919</v>
+        <v>44937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45919</v>
+        <v>44973</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45919</v>
+        <v>45905</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45303</v>
+        <v>45919</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1784,13 +1784,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1833,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1847,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44912</v>
+        <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1863,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1906,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1920,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46154</v>
+        <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1936,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1979,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1993,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45063</v>
+        <v>44912</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2009,7 +2004,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2052,7 +2047,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2066,10 +2061,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45977</v>
+        <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2082,7 +2077,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2125,7 +2120,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2139,10 +2134,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45981</v>
+        <v>45303</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2154,8 +2149,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44973</v>
+        <v>45063</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46036</v>
+        <v>45977</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46036</v>
+        <v>44973</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44912</v>
+        <v>45981</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46075</v>
+        <v>45666</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46079</v>
+        <v>45260</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46079</v>
+        <v>46036</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44896</v>
+        <v>46036</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44973</v>
+        <v>46283</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46246</v>
+        <v>45631</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2938,14 +2938,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44937</v>
+        <v>46075</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45260</v>
+        <v>46246</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46251</v>
+        <v>46079</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7.7</v>
+        <v>2.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46126</v>
+        <v>46079</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44896</v>
+        <v>45791</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>7.5</v>
+        <v>4.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 34394-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46253</v>
+        <v>45846</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 32577-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45791</v>
+        <v>45838</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45062</v>
+        <v>45847</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44910</v>
+        <v>46126</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46275</v>
+        <v>44896</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46275</v>
+        <v>44912</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46279</v>
+        <v>46154</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>7.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46280</v>
+        <v>46251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.9</v>
+        <v>7.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45987</v>
+        <v>46253</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46283</v>
+        <v>45062</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45631</v>
+        <v>45791</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45791</v>
+        <v>44910</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45791</v>
+        <v>46275</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45666</v>
+        <v>46275</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45847</v>
+        <v>46279</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 34394-2025</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45846</v>
+        <v>45987</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32577-2025</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45838</v>
+        <v>46280</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46029</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45791</v>
+        <v>45905</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44937</v>
+        <v>45919</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44973</v>
+        <v>45919</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45905</v>
+        <v>45919</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45919</v>
+        <v>45303</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1784,8 +1784,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1833,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1847,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45919</v>
+        <v>44912</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1863,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1906,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1920,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45919</v>
+        <v>45063</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1931,7 +1936,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1979,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1993,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44912</v>
+        <v>45977</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2004,7 +2009,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2052,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2066,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44896</v>
+        <v>45981</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2082,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2125,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2139,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45303</v>
+        <v>44973</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2149,13 +2154,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45063</v>
+        <v>46154</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45977</v>
+        <v>46036</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44973</v>
+        <v>46036</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.7</v>
+        <v>1.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45981</v>
+        <v>44912</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45666</v>
+        <v>46075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45260</v>
+        <v>46079</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46036</v>
+        <v>46079</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46036</v>
+        <v>44896</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46283</v>
+        <v>44973</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2865,14 +2865,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45631</v>
+        <v>44937</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46075</v>
+        <v>45260</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46246</v>
+        <v>46126</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46079</v>
+        <v>44896</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46079</v>
+        <v>46251</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>7.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45791</v>
+        <v>46253</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 34394-2025</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45846</v>
+        <v>45791</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32577-2025</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45838</v>
+        <v>45062</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45847</v>
+        <v>44910</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46126</v>
+        <v>46275</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44896</v>
+        <v>45631</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44912</v>
+        <v>46275</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46154</v>
+        <v>46279</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>7.3</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46251</v>
+        <v>46280</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>7.7</v>
+        <v>2.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46253</v>
+        <v>45987</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45062</v>
+        <v>46283</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4040,7 +4040,7 @@
         <v>45791</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44910</v>
+        <v>45791</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46275</v>
+        <v>46246</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46275</v>
+        <v>45666</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46279</v>
+        <v>45847</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 34394-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45987</v>
+        <v>45846</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 32577-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46280</v>
+        <v>45838</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 34591-2022</t>
+          <t>A 889-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44795</v>
+        <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -992,58 +992,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Blågrönt mannagräs</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 889-2026</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46029</v>
+        <v>46075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,20 +1073,20 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
@@ -1097,58 +1097,58 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46075</v>
+        <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1202,10 +1202,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1218,42 +1218,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="I8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1323,42 +1323,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 34591-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46080</v>
+        <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,20 +1388,20 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1428,42 +1428,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blågrönt mannagräs</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1473,14 +1473,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45905</v>
+        <v>44937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45919</v>
+        <v>46036</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45919</v>
+        <v>46036</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45919</v>
+        <v>44912</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45303</v>
+        <v>45905</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1784,13 +1784,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1833,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1847,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44912</v>
+        <v>44896</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1863,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1906,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1920,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45063</v>
+        <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1936,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1979,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1993,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45977</v>
+        <v>45919</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2009,7 +2004,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2052,7 +2047,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2066,10 +2061,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45981</v>
+        <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2082,7 +2077,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2125,7 +2120,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2139,10 +2134,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44973</v>
+        <v>46075</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2155,7 +2150,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2193,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2212,10 +2207,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46154</v>
+        <v>46079</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2228,7 +2223,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.3</v>
+        <v>2.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2266,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2280,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46036</v>
+        <v>46079</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2296,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2339,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2353,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46036</v>
+        <v>45303</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2373,8 +2368,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44912</v>
+        <v>45063</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46075</v>
+        <v>44973</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>5.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46079</v>
+        <v>46126</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46079</v>
+        <v>45977</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44896</v>
+        <v>45981</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44973</v>
+        <v>45666</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2865,14 +2865,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44937</v>
+        <v>46154</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.2</v>
+        <v>7.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 34394-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45260</v>
+        <v>45846</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 32577-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46126</v>
+        <v>45838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44896</v>
+        <v>44973</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7.5</v>
+        <v>3.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46251</v>
+        <v>45847</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>7.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45791</v>
+        <v>46253</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45062</v>
+        <v>45260</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44910</v>
+        <v>45062</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46275</v>
+        <v>45791</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45631</v>
+        <v>44910</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>46275</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45987</v>
+        <v>45631</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45791</v>
+        <v>46283</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4113,7 +4113,7 @@
         <v>45791</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46246</v>
+        <v>45987</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45666</v>
+        <v>46246</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45847</v>
+        <v>44896</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 34394-2025</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45846</v>
+        <v>44912</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32577-2025</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45838</v>
+        <v>45791</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>44937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>46036</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>46036</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44912</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45905</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>44896</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45919</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>46075</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>46079</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>46079</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45303</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>45063</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>44973</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>46126</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>45977</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45981</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>45666</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>46154</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45846</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>45838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44973</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>45847</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46251</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>46253</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45260</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45062</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45791</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44910</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>46275</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>46275</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>46279</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>45631</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>46280</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>46283</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>45791</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>45987</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46246</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>44896</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>44912</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>45791</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>44937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>46036</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>46036</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44912</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45905</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>44896</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45919</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>46075</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>46079</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>46079</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45303</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>45063</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>44973</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>46126</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>45977</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45981</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>45666</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>46154</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45846</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>45838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44973</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>45847</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46251</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>46253</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45260</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45062</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45791</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44910</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>46275</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>46275</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>46279</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>45631</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>46280</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>46283</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>45791</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>45987</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46246</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>44896</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>44912</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>45791</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 34591-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46075</v>
+        <v>44795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1113,42 +1113,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Blågrönt mannagräs</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46080</v>
+        <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,34 +1178,34 @@
         </is>
       </c>
       <c r="I7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="n">
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1218,42 +1218,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1323,42 +1323,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 34591-2022</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44795</v>
+        <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,19 +1388,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1428,42 +1428,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Blågrönt mannagräs</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1473,14 +1473,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44937</v>
+        <v>45791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46036</v>
+        <v>45905</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46036</v>
+        <v>45919</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44912</v>
+        <v>45919</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45905</v>
+        <v>45919</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44896</v>
+        <v>45666</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.5</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45919</v>
+        <v>45303</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1930,8 +1930,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1979,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1993,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45919</v>
+        <v>45847</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2004,7 +2009,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2052,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 34394-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2066,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45919</v>
+        <v>45846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2082,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2125,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 32577-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2139,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46075</v>
+        <v>45838</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2150,7 +2155,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2193,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2207,10 +2212,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46079</v>
+        <v>46036</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2223,7 +2228,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2266,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2280,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46079</v>
+        <v>46036</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2296,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2339,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2353,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45303</v>
+        <v>45977</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2368,13 +2373,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45063</v>
+        <v>45981</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44973</v>
+        <v>46075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46126</v>
+        <v>46079</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45977</v>
+        <v>46079</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45981</v>
+        <v>44912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45666</v>
+        <v>45063</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46154</v>
+        <v>46126</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>7.3</v>
+        <v>4.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 34394-2025</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45846</v>
+        <v>44973</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32577-2025</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45838</v>
+        <v>44912</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44973</v>
+        <v>46154</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.1</v>
+        <v>7.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45847</v>
+        <v>44896</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46251</v>
+        <v>44973</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>7.7</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3303,14 +3303,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46253</v>
+        <v>44937</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>45260</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45062</v>
+        <v>44896</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45791</v>
+        <v>46253</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44910</v>
+        <v>45791</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46275</v>
+        <v>45062</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46275</v>
+        <v>45631</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46279</v>
+        <v>44910</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45631</v>
+        <v>46275</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46280</v>
+        <v>46275</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46283</v>
+        <v>46279</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45791</v>
+        <v>46280</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45987</v>
+        <v>46283</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46246</v>
+        <v>45791</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44896</v>
+        <v>46246</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44912</v>
+        <v>46251</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45791</v>
+        <v>45987</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 34591-2022</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44795</v>
+        <v>46075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1113,42 +1113,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Blågrönt mannagräs</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46075</v>
+        <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1202,10 +1202,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1218,42 +1218,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="I8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1323,42 +1323,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 34591-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46080</v>
+        <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,20 +1388,20 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1428,35 +1428,35 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blågrönt mannagräs</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
         <v>45791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45905</v>
+        <v>44937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45919</v>
+        <v>44912</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45919</v>
+        <v>45905</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45919</v>
+        <v>44896</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>7.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45666</v>
+        <v>46036</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45303</v>
+        <v>46036</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1930,13 +1930,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1979,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1993,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45847</v>
+        <v>45919</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2009,7 +2004,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2052,7 +2047,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 34394-2025</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2066,10 +2061,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45846</v>
+        <v>45666</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2082,7 +2077,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2125,7 +2120,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32577-2025</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2139,10 +2134,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45838</v>
+        <v>45919</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2155,7 +2150,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2193,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2212,10 +2207,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46036</v>
+        <v>45919</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2228,7 +2223,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2266,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2280,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46036</v>
+        <v>45303</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2300,8 +2295,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 34394-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45977</v>
+        <v>45846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 32577-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45981</v>
+        <v>45838</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46075</v>
+        <v>45847</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46079</v>
+        <v>45063</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46079</v>
+        <v>44973</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44912</v>
+        <v>45977</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45063</v>
+        <v>45981</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46126</v>
+        <v>46075</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44973</v>
+        <v>46079</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44912</v>
+        <v>46079</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46154</v>
+        <v>46126</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7.3</v>
+        <v>4.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44896</v>
+        <v>44973</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44973</v>
+        <v>46154</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.1</v>
+        <v>7.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3303,14 +3303,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44937</v>
+        <v>45260</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45260</v>
+        <v>45631</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44896</v>
+        <v>46253</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.5</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46253</v>
+        <v>44896</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45791</v>
+        <v>44912</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>45062</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45631</v>
+        <v>45791</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         <v>44910</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3894,7 +3894,7 @@
         <v>46275</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3967,7 +3967,7 @@
         <v>46275</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4040,7 +4040,7 @@
         <v>46279</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>46280</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>46283</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45791</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>46246</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46251</v>
+        <v>45987</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>7.7</v>
+        <v>2.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45987</v>
+        <v>46251</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.7</v>
+        <v>7.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 889-2026</t>
+          <t>A 34591-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46029</v>
+        <v>44795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -968,20 +968,20 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
@@ -992,58 +992,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blågrönt mannagräs</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 889-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46075</v>
+        <v>46029</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1097,58 +1097,58 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46080</v>
+        <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,34 +1178,34 @@
         </is>
       </c>
       <c r="I7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="n">
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1218,42 +1218,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1323,42 +1323,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 34591-2022</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44795</v>
+        <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,19 +1388,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1428,42 +1428,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Blågrönt mannagräs</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45791</v>
+        <v>44912</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44937</v>
+        <v>44896</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44912</v>
+        <v>45631</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45905</v>
+        <v>44973</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1765,14 +1765,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44896</v>
+        <v>44937</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.5</v>
+        <v>0.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46036</v>
+        <v>45260</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46036</v>
+        <v>44912</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45919</v>
+        <v>44896</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>7.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45666</v>
+        <v>45063</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2120,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45919</v>
+        <v>45791</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2193,7 +2193,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45919</v>
+        <v>44973</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45303</v>
+        <v>45666</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2295,13 +2295,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2339,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 34394-2025</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2353,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45846</v>
+        <v>45847</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2369,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2412,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32577-2025</t>
+          <t>A 34394-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2426,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45838</v>
+        <v>45846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2442,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2485,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 32577-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2499,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45847</v>
+        <v>45838</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2515,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2558,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2572,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45063</v>
+        <v>45905</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2588,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2631,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2645,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44973</v>
+        <v>45919</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2661,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.7</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2704,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2718,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45977</v>
+        <v>45919</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2734,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2777,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2791,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45981</v>
+        <v>45919</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2807,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2850,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2864,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46075</v>
+        <v>45977</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2880,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2923,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2937,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46079</v>
+        <v>45981</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2953,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +2996,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3010,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46079</v>
+        <v>45303</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3030,8 +3025,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46126</v>
+        <v>46036</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44973</v>
+        <v>46036</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46154</v>
+        <v>46075</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>7.3</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45260</v>
+        <v>46079</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45631</v>
+        <v>46079</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46253</v>
+        <v>46126</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44896</v>
+        <v>46154</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>7.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44912</v>
+        <v>45791</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>45062</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45791</v>
+        <v>44910</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44910</v>
+        <v>46275</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3894,7 +3894,7 @@
         <v>46275</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46283</v>
+        <v>45791</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45791</v>
+        <v>46246</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46246</v>
+        <v>45987</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45987</v>
+        <v>46253</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4478,7 +4478,7 @@
         <v>46251</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 34591-2022</t>
+          <t>A 889-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44795</v>
+        <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -992,58 +992,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Blågrönt mannagräs</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 889-2026</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46029</v>
+        <v>46075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,20 +1073,20 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
@@ -1097,58 +1097,58 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46075</v>
+        <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1202,10 +1202,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1218,42 +1218,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="I8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1323,42 +1323,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 34591-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46080</v>
+        <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,20 +1388,20 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1428,42 +1428,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blågrönt mannagräs</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44912</v>
+        <v>45791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44896</v>
+        <v>44937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45631</v>
+        <v>46036</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44973</v>
+        <v>46036</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1765,14 +1765,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44937</v>
+        <v>45905</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45260</v>
+        <v>44912</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44912</v>
+        <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44896</v>
+        <v>45919</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>7.5</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45063</v>
+        <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2120,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45791</v>
+        <v>44896</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2193,7 +2193,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44973</v>
+        <v>46075</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45666</v>
+        <v>46079</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2339,7 +2339,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45847</v>
+        <v>46079</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 34394-2025</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45846</v>
+        <v>45303</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2441,8 +2441,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2485,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32577-2025</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2499,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45838</v>
+        <v>45063</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2515,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2558,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2572,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45905</v>
+        <v>45977</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2631,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2645,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45919</v>
+        <v>46126</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2661,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2704,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2718,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45919</v>
+        <v>45981</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2734,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2777,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2791,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45919</v>
+        <v>44973</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2807,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>5.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2850,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2864,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45977</v>
+        <v>45666</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2880,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2923,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 34394-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2937,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45981</v>
+        <v>45846</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2953,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2996,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 32577-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3010,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45303</v>
+        <v>45838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3025,13 +3030,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46036</v>
+        <v>45847</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46036</v>
+        <v>46154</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>7.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46075</v>
+        <v>44973</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46079</v>
+        <v>45260</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46079</v>
+        <v>45062</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46126</v>
+        <v>45631</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46154</v>
+        <v>45791</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7.3</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45791</v>
+        <v>44910</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45062</v>
+        <v>46275</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44910</v>
+        <v>46275</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46280</v>
+        <v>45791</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46283</v>
+        <v>46246</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45791</v>
+        <v>45987</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46246</v>
+        <v>44896</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45987</v>
+        <v>44912</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>7.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7.7</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>45791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44937</v>
+        <v>46036</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46036</v>
+        <v>45905</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1699,7 +1699,7 @@
         <v>46036</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45905</v>
+        <v>45919</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44912</v>
+        <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1918,7 +1918,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45919</v>
+        <v>45303</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2003,8 +2003,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2052,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2066,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45919</v>
+        <v>46075</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2082,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2125,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2139,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44896</v>
+        <v>46079</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2150,7 +2155,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.5</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2193,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2207,10 +2212,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46075</v>
+        <v>46079</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2223,7 +2228,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2266,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2280,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46079</v>
+        <v>45977</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2296,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2339,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2353,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46079</v>
+        <v>45981</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2369,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2412,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2426,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45303</v>
+        <v>46126</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2441,13 +2446,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45063</v>
+        <v>45666</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45977</v>
+        <v>44912</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46126</v>
+        <v>45847</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 34394-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45981</v>
+        <v>45846</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 32577-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44973</v>
+        <v>45838</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45666</v>
+        <v>45063</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 34394-2025</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45846</v>
+        <v>44973</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32577-2025</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45838</v>
+        <v>46154</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.3</v>
+        <v>7.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45847</v>
+        <v>44912</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46154</v>
+        <v>44896</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.3</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
         <v>44973</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3303,14 +3303,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45260</v>
+        <v>44937</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45062</v>
+        <v>45260</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45631</v>
+        <v>45791</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45791</v>
+        <v>45062</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3602,7 +3602,7 @@
         <v>44910</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46275</v>
+        <v>44896</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>46275</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45791</v>
+        <v>46283</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46246</v>
+        <v>45791</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45987</v>
+        <v>46246</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44896</v>
+        <v>45987</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44912</v>
+        <v>46251</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>7.7</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46253</v>
+        <v>45631</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>45791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>46036</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45905</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>46036</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45919</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45303</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46075</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>46079</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>46079</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45977</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>45981</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>46126</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45666</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>44912</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>45847</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45846</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>45838</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>45063</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>44973</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>46154</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44912</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>44896</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>44973</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>44937</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45260</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45791</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45062</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44910</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44896</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>46275</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>46275</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>46279</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>46280</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>46283</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>45791</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>46246</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45987</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>46251</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>46253</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>45631</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>45791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>46036</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45905</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>46036</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45919</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45303</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46075</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>46079</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>46079</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45977</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>45981</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>46126</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45666</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>44912</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>45847</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45846</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>45838</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>45063</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>44973</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>46154</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44912</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>44896</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>44973</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>44937</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45260</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45791</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45062</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44910</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44896</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>46275</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>46275</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>46279</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>46280</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>46283</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>45791</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>46246</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45987</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>46251</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>46253</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>45631</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE51"/>
+  <dimension ref="A1:AE49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 889-2026</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46029</v>
+        <v>46075</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -968,20 +968,20 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
@@ -992,58 +992,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46075</v>
+        <v>46080</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1097,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1113,42 +1113,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1165,7 +1165,7 @@
         <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,13 +1178,13 @@
         </is>
       </c>
       <c r="I7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1218,42 +1218,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 889-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46080</v>
+        <v>46029</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1316,42 +1316,42 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
         <v/>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1473,14 +1473,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45791</v>
+        <v>44937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1553,7 +1553,7 @@
         <v>46036</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45905</v>
+        <v>44912</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46036</v>
+        <v>44896</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>7.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45919</v>
+        <v>45666</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45919</v>
+        <v>45905</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45919</v>
+        <v>45063</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>5.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45303</v>
+        <v>45919</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2003,13 +2003,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2052,7 +2047,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2066,10 +2061,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46075</v>
+        <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2082,7 +2077,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2125,7 +2120,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2139,10 +2134,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46079</v>
+        <v>45919</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2155,7 +2150,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2193,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2212,10 +2207,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46079</v>
+        <v>45303</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2227,8 +2222,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45977</v>
+        <v>44973</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>5.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45981</v>
+        <v>46075</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46126</v>
+        <v>46079</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45666</v>
+        <v>46079</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44912</v>
+        <v>45977</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45847</v>
+        <v>45981</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 34394-2025</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45846</v>
+        <v>46126</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32577-2025</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45838</v>
+        <v>44973</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45063</v>
+        <v>46036</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.8</v>
+        <v>2.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44973</v>
+        <v>46154</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5.7</v>
+        <v>7.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46154</v>
+        <v>45260</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7.3</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44912</v>
+        <v>45631</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44896</v>
+        <v>45062</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44973</v>
+        <v>45791</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3303,14 +3303,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44937</v>
+        <v>44910</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.2</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45260</v>
+        <v>46275</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45791</v>
+        <v>46275</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45062</v>
+        <v>46279</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44910</v>
+        <v>44896</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44896</v>
+        <v>44912</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>7.5</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46279</v>
+        <v>45791</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46280</v>
+        <v>46246</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46283</v>
+        <v>45987</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45791</v>
+        <v>46251</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.6</v>
+        <v>7.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45987</v>
+        <v>45847</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4312,10 +4312,10 @@
       </c>
       <c r="V48" s="2" t="inlineStr"/>
     </row>
-    <row r="49" ht="15" customHeight="1">
+    <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46251</v>
+        <v>45791</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>7.7</v>
+        <v>2.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4384,152 +4384,6 @@
         <v>0</v>
       </c>
       <c r="V49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>A 34198-2026</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="n">
-        <v>46253</v>
-      </c>
-      <c r="E50" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>TJÖRN</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>A 57955-2024</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="n">
-        <v>45631</v>
-      </c>
-      <c r="E51" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>TJÖRN</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 889-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46075</v>
+        <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -992,58 +992,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46080</v>
+        <v>46075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,34 +1073,34 @@
         </is>
       </c>
       <c r="I6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="n">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1113,42 +1113,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1165,7 +1165,7 @@
         <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,13 +1178,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1218,42 +1218,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 889-2026</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46029</v>
+        <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1316,42 +1316,42 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1473,14 +1473,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44937</v>
+        <v>46036</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>46036</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44912</v>
+        <v>45905</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44896</v>
+        <v>45919</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.5</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45666</v>
+        <v>45919</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45905</v>
+        <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45063</v>
+        <v>46075</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45919</v>
+        <v>46079</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45919</v>
+        <v>46079</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2120,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45919</v>
+        <v>45666</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2210,7 +2210,7 @@
         <v>45303</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44973</v>
+        <v>46126</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46075</v>
+        <v>45977</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46079</v>
+        <v>45981</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46079</v>
+        <v>46154</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>7.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45977</v>
+        <v>44912</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45981</v>
+        <v>45063</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46126</v>
+        <v>44973</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44973</v>
+        <v>44912</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46036</v>
+        <v>45791</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46154</v>
+        <v>45062</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>7.3</v>
+        <v>3.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45260</v>
+        <v>44910</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45631</v>
+        <v>46275</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45062</v>
+        <v>46275</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45791</v>
+        <v>44896</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44910</v>
+        <v>46279</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46275</v>
+        <v>44973</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3595,14 +3595,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44896</v>
+        <v>44937</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44912</v>
+        <v>45260</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46280</v>
+        <v>45791</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46283</v>
+        <v>46246</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45791</v>
+        <v>44896</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.6</v>
+        <v>7.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46246</v>
+        <v>45987</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45987</v>
+        <v>46251</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.7</v>
+        <v>7.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>7.7</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46253</v>
+        <v>45847</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45847</v>
+        <v>45631</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4332,7 +4332,7 @@
         <v>45791</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 889-2026</t>
+          <t>A 34591-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46029</v>
+        <v>44795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -968,20 +968,20 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
@@ -992,58 +992,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blågrönt mannagräs</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 889-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46075</v>
+        <v>46029</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1097,58 +1097,58 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46080</v>
+        <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,34 +1178,34 @@
         </is>
       </c>
       <c r="I7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="n">
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1218,42 +1218,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1323,42 +1323,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 34591-2022</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44795</v>
+        <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,19 +1388,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1428,42 +1428,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Blågrönt mannagräs</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46036</v>
+        <v>45791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46036</v>
+        <v>44937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1626,7 +1626,7 @@
         <v>45905</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45919</v>
+        <v>44973</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1772,7 +1772,7 @@
         <v>45919</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
         <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46075</v>
+        <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46079</v>
+        <v>45303</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2003,8 +2003,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2052,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2066,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46079</v>
+        <v>45666</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2082,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2125,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2139,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45666</v>
+        <v>44912</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2150,7 +2155,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2193,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2207,10 +2212,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45303</v>
+        <v>44896</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2222,13 +2227,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46126</v>
+        <v>45977</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45977</v>
+        <v>45063</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.3</v>
+        <v>5.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2434,7 +2434,7 @@
         <v>45981</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>46154</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44912</v>
+        <v>44973</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>5.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45063</v>
+        <v>45260</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44973</v>
+        <v>46036</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5.7</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44912</v>
+        <v>46036</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45791</v>
+        <v>45631</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45062</v>
+        <v>46075</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44910</v>
+        <v>46079</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46275</v>
+        <v>46079</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46275</v>
+        <v>46126</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
         <v>44896</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46279</v>
+        <v>44912</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44973</v>
+        <v>45062</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46280</v>
+        <v>45791</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46283</v>
+        <v>44910</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3595,14 +3595,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44937</v>
+        <v>46275</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45260</v>
+        <v>46275</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45791</v>
+        <v>46279</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46246</v>
+        <v>46280</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44896</v>
+        <v>46283</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45987</v>
+        <v>45791</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46251</v>
+        <v>46246</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7.7</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46253</v>
+        <v>45987</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45847</v>
+        <v>46251</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>7.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45631</v>
+        <v>46253</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45791</v>
+        <v>45847</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46029</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45791</v>
+        <v>45905</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44937</v>
+        <v>45919</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45905</v>
+        <v>45919</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44973</v>
+        <v>45919</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45919</v>
+        <v>45303</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1784,8 +1784,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1833,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1847,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45919</v>
+        <v>44912</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1863,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1906,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1920,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45919</v>
+        <v>45063</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1931,7 +1936,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1979,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1993,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45303</v>
+        <v>46126</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2003,13 +2008,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45666</v>
+        <v>45977</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2125,7 +2125,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2139,10 +2139,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44912</v>
+        <v>45981</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44896</v>
+        <v>44973</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45977</v>
+        <v>46036</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45063</v>
+        <v>46036</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.8</v>
+        <v>1.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45981</v>
+        <v>44912</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46154</v>
+        <v>46075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.3</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44973</v>
+        <v>46079</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.7</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45260</v>
+        <v>46079</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46036</v>
+        <v>44896</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46036</v>
+        <v>44973</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45631</v>
+        <v>46154</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>7.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2938,14 +2938,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46075</v>
+        <v>44937</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46079</v>
+        <v>45260</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46079</v>
+        <v>44896</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>7.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46126</v>
+        <v>45791</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44896</v>
+        <v>45062</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44912</v>
+        <v>45631</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45062</v>
+        <v>44910</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45791</v>
+        <v>46275</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44910</v>
+        <v>46275</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46280</v>
+        <v>45791</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46283</v>
+        <v>45791</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45791</v>
+        <v>46246</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46246</v>
+        <v>45987</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45987</v>
+        <v>46251</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.7</v>
+        <v>7.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46251</v>
+        <v>45666</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.7</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4259,7 +4259,7 @@
         <v>46253</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45847</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE49"/>
+  <dimension ref="A1:AE50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46029</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45905</v>
+        <v>44896</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45919</v>
+        <v>44912</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1619,14 +1619,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45919</v>
+        <v>44937</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45919</v>
+        <v>44973</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45303</v>
+        <v>45905</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1784,13 +1784,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1850,7 +1845,7 @@
         <v>44912</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1906,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1920,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45063</v>
+        <v>44896</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1936,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1979,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1993,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46126</v>
+        <v>45919</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2009,7 +2004,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2052,7 +2047,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2066,10 +2061,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45977</v>
+        <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2082,7 +2077,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2125,7 +2120,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2139,10 +2134,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45981</v>
+        <v>45919</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2155,7 +2150,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2193,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2212,10 +2207,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44973</v>
+        <v>45791</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2228,7 +2223,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2266,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2280,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46036</v>
+        <v>45303</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2300,8 +2295,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46036</v>
+        <v>45063</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44912</v>
+        <v>45666</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46075</v>
+        <v>44973</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>5.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46079</v>
+        <v>45977</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46079</v>
+        <v>45260</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44896</v>
+        <v>45981</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44973</v>
+        <v>45631</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46154</v>
+        <v>46126</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>7.3</v>
+        <v>4.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2938,14 +2938,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44937</v>
+        <v>46036</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45260</v>
+        <v>46036</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44896</v>
+        <v>46075</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45791</v>
+        <v>46079</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45062</v>
+        <v>46079</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45631</v>
+        <v>46154</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>7.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44910</v>
+        <v>45062</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46275</v>
+        <v>45791</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46275</v>
+        <v>44910</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46280</v>
+        <v>46275</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46283</v>
+        <v>46279</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45791</v>
+        <v>46280</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45791</v>
+        <v>46283</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46246</v>
+        <v>45791</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45987</v>
+        <v>46246</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46251</v>
+        <v>45987</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>7.7</v>
+        <v>2.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45666</v>
+        <v>46251</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>7.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4259,7 +4259,7 @@
         <v>46253</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="V48" s="2" t="inlineStr"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
           <t>A 34508-2025</t>
@@ -4332,7 +4332,7 @@
         <v>45847</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4384,6 +4384,79 @@
         <v>0</v>
       </c>
       <c r="V49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>A 41950-2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>TJÖRN</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46029</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>44896</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>44912</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>44937</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44973</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45905</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>44912</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>44896</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45919</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>45919</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45791</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>45303</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>45063</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>45666</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>44973</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>45977</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>45260</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45981</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>45631</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>46126</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>46036</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>46036</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>46075</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>46079</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46079</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>46154</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45062</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45791</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44910</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>46275</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>46275</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>46279</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>46280</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>46283</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45791</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>46246</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>45987</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>46251</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46253</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45847</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>46303</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46029</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>44896</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>44912</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>44937</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44973</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45905</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>44912</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>44896</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45919</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>45919</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45791</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>45303</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>45063</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>45666</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>44973</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>45977</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>45260</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45981</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>45631</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>46126</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>46036</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>46036</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>46075</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>46079</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46079</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>46154</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45062</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45791</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44910</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>46275</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>46275</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>46279</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>46280</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>46283</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45791</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>46246</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>45987</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>46251</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46253</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45847</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>46303</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 34591-2022</t>
+          <t>A 889-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44795</v>
+        <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -992,58 +992,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Blågrönt mannagräs</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 889-2026</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46029</v>
+        <v>46075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,20 +1073,20 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
@@ -1097,58 +1097,58 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46075</v>
+        <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1202,10 +1202,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1218,42 +1218,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="I8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1323,42 +1323,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 34591-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46080</v>
+        <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,20 +1388,20 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1428,42 +1428,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blågrönt mannagräs</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44896</v>
+        <v>45905</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44912</v>
+        <v>45919</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1619,14 +1619,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44937</v>
+        <v>45919</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44973</v>
+        <v>45919</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45905</v>
+        <v>45631</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44912</v>
+        <v>45303</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1857,8 +1857,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1906,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1920,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44896</v>
+        <v>45977</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1931,7 +1936,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1979,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1993,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45919</v>
+        <v>45981</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2004,7 +2009,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2052,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2066,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45919</v>
+        <v>45791</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2082,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2125,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2139,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45919</v>
+        <v>45791</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2150,7 +2155,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2193,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2207,10 +2212,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45791</v>
+        <v>45062</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2223,7 +2228,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2266,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2280,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45303</v>
+        <v>44910</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2295,13 +2300,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45063</v>
+        <v>46275</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45666</v>
+        <v>46275</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44973</v>
+        <v>46279</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45977</v>
+        <v>45666</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45260</v>
+        <v>46280</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45981</v>
+        <v>46036</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45631</v>
+        <v>46036</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46126</v>
+        <v>46283</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46036</v>
+        <v>45791</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46036</v>
+        <v>46246</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46075</v>
+        <v>45987</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46079</v>
+        <v>46075</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
         <v>46079</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46154</v>
+        <v>46079</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>7.3</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45062</v>
+        <v>46251</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.4</v>
+        <v>7.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45791</v>
+        <v>46253</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44910</v>
+        <v>45847</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46275</v>
+        <v>46126</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 41950-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46275</v>
+        <v>46303</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46279</v>
+        <v>46154</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>7.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46280</v>
+        <v>44912</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46283</v>
+        <v>45063</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45791</v>
+        <v>44973</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46246</v>
+        <v>44912</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45987</v>
+        <v>44896</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46251</v>
+        <v>44973</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.7</v>
+        <v>3.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4252,14 +4252,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46253</v>
+        <v>44937</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45847</v>
+        <v>45260</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 41950-2026</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46303</v>
+        <v>44896</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>7.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45905</v>
+        <v>45791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45919</v>
+        <v>44937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45919</v>
+        <v>45905</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45919</v>
+        <v>44912</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45631</v>
+        <v>45919</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45303</v>
+        <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1857,13 +1857,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1906,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1920,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45977</v>
+        <v>45666</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1936,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1979,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1993,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45981</v>
+        <v>45919</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2009,7 +2004,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2052,7 +2047,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2066,10 +2061,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45791</v>
+        <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2082,7 +2077,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2125,7 +2120,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2139,10 +2134,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45791</v>
+        <v>45303</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2154,8 +2149,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45062</v>
+        <v>46036</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44910</v>
+        <v>46036</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46275</v>
+        <v>45063</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46275</v>
+        <v>45977</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46279</v>
+        <v>45981</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45666</v>
+        <v>44973</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46280</v>
+        <v>46075</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46036</v>
+        <v>46079</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46036</v>
+        <v>46079</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46283</v>
+        <v>46126</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45791</v>
+        <v>44973</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46246</v>
+        <v>46154</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>7.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45987</v>
+        <v>45260</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46075</v>
+        <v>45631</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46079</v>
+        <v>45062</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46079</v>
+        <v>45791</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46251</v>
+        <v>44910</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7.7</v>
+        <v>4.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46253</v>
+        <v>46275</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45847</v>
+        <v>46275</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46126</v>
+        <v>46279</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 41950-2026</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46303</v>
+        <v>44896</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46154</v>
+        <v>44912</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>7.3</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44912</v>
+        <v>46280</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45063</v>
+        <v>46283</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.8</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44973</v>
+        <v>45791</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44912</v>
+        <v>46246</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44896</v>
+        <v>45987</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44973</v>
+        <v>46251</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.1</v>
+        <v>7.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4252,14 +4252,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44937</v>
+        <v>46253</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45260</v>
+        <v>45847</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 41950-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44896</v>
+        <v>46303</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>7.5</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 889-2026</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46029</v>
+        <v>46075</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -968,20 +968,20 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
@@ -992,58 +992,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46075</v>
+        <v>46080</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1097,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1113,42 +1113,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1165,7 +1165,7 @@
         <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,13 +1178,13 @@
         </is>
       </c>
       <c r="I7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1218,42 +1218,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 889-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46080</v>
+        <v>46029</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1316,42 +1316,42 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
         <v/>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45791</v>
+        <v>45063</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44937</v>
+        <v>45666</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1626,7 +1626,7 @@
         <v>45905</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44912</v>
+        <v>45919</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1772,7 +1772,7 @@
         <v>45919</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
         <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45666</v>
+        <v>45303</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1930,8 +1930,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1979,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1993,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45919</v>
+        <v>46075</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2004,7 +2009,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2052,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2066,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44896</v>
+        <v>46079</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2082,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.5</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2125,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2139,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45303</v>
+        <v>46079</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2149,13 +2154,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46036</v>
+        <v>44973</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46036</v>
+        <v>45977</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45063</v>
+        <v>45981</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45977</v>
+        <v>46126</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45981</v>
+        <v>46036</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44973</v>
+        <v>46036</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.7</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46075</v>
+        <v>44912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46079</v>
+        <v>46154</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>7.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46079</v>
+        <v>44912</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46126</v>
+        <v>44896</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
         <v>44973</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3011,14 +3011,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46154</v>
+        <v>44937</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7.3</v>
+        <v>0.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>45260</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45631</v>
+        <v>44896</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45062</v>
+        <v>45791</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45791</v>
+        <v>45062</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>44910</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3456,7 +3456,7 @@
         <v>46275</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3529,7 +3529,7 @@
         <v>46275</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3602,7 +3602,7 @@
         <v>46279</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44896</v>
+        <v>46280</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44912</v>
+        <v>46283</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46280</v>
+        <v>45791</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46283</v>
+        <v>46246</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45791</v>
+        <v>45987</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>7.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45987</v>
+        <v>45631</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.7</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46253</v>
+        <v>45847</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 41950-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45847</v>
+        <v>46303</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 41950-2026</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46303</v>
+        <v>45791</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 34591-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46075</v>
+        <v>44795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1008,42 +1008,42 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Blågrönt mannagräs</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 889-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46080</v>
+        <v>46029</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1106,49 +1106,49 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46080</v>
+        <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,20 +1178,20 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
@@ -1202,10 +1202,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1218,42 +1218,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 889-2026</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46029</v>
+        <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1316,49 +1316,49 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 34591-2022</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44795</v>
+        <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,19 +1388,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1428,42 +1428,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Blågrönt mannagräs</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45063</v>
+        <v>45666</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45666</v>
+        <v>44937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45905</v>
+        <v>44973</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45919</v>
+        <v>44912</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45919</v>
+        <v>44896</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45919</v>
+        <v>46126</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45303</v>
+        <v>45063</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1930,13 +1930,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1979,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1993,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46075</v>
+        <v>45905</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2009,7 +2004,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2052,7 +2047,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2066,10 +2061,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46079</v>
+        <v>44973</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2082,7 +2077,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2125,7 +2120,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2139,10 +2134,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46079</v>
+        <v>46154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2155,7 +2150,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.9</v>
+        <v>7.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2193,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2212,10 +2207,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44973</v>
+        <v>45260</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2228,7 +2223,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2266,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2280,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45977</v>
+        <v>45919</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2296,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2339,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2353,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45981</v>
+        <v>45919</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2369,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2412,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2426,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46126</v>
+        <v>45919</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2442,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2485,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2499,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46036</v>
+        <v>45631</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2515,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2558,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2572,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46036</v>
+        <v>45303</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2592,8 +2587,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44912</v>
+        <v>44896</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46154</v>
+        <v>44912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.3</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44912</v>
+        <v>45062</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44896</v>
+        <v>45791</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44973</v>
+        <v>44910</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3011,14 +3011,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44937</v>
+        <v>46275</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45260</v>
+        <v>46275</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44896</v>
+        <v>46279</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45791</v>
+        <v>46280</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45062</v>
+        <v>45977</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44910</v>
+        <v>46283</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46275</v>
+        <v>45791</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46275</v>
+        <v>46246</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46279</v>
+        <v>45981</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46280</v>
+        <v>46251</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.9</v>
+        <v>7.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46283</v>
+        <v>46253</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45791</v>
+        <v>45847</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46246</v>
+        <v>45791</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 41950-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45987</v>
+        <v>46303</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46251</v>
+        <v>46036</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7.7</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45631</v>
+        <v>46036</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46253</v>
+        <v>45987</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45847</v>
+        <v>46075</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 41950-2026</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46303</v>
+        <v>46079</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45791</v>
+        <v>46079</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46029</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45666</v>
+        <v>45905</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44937</v>
+        <v>45919</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44973</v>
+        <v>45919</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44912</v>
+        <v>45919</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44896</v>
+        <v>44912</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46126</v>
+        <v>45303</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1857,8 +1857,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1918,7 +1923,7 @@
         <v>45063</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1974,7 +1979,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1993,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45905</v>
+        <v>46154</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2004,7 +2009,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2052,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2066,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44973</v>
+        <v>45977</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2082,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2125,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2139,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46154</v>
+        <v>45981</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2150,7 +2155,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.3</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2193,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2207,10 +2212,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45260</v>
+        <v>44973</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2223,7 +2228,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>5.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2266,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2280,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45919</v>
+        <v>44912</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2296,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2339,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2353,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45919</v>
+        <v>46036</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2369,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2412,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2426,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45919</v>
+        <v>46036</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2442,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2485,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2499,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45631</v>
+        <v>46075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2515,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2558,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2572,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45303</v>
+        <v>46079</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2587,13 +2592,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44896</v>
+        <v>46079</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44912</v>
+        <v>44896</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45062</v>
+        <v>44973</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2865,14 +2865,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45791</v>
+        <v>44937</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44910</v>
+        <v>45260</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46275</v>
+        <v>46126</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46275</v>
+        <v>44896</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46279</v>
+        <v>45791</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46280</v>
+        <v>45062</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45977</v>
+        <v>44910</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45791</v>
+        <v>46275</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46246</v>
+        <v>46279</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45981</v>
+        <v>46280</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46251</v>
+        <v>46283</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>7.7</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46253</v>
+        <v>45791</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45847</v>
+        <v>46246</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45791</v>
+        <v>45631</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 41950-2026</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46303</v>
+        <v>46251</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46036</v>
+        <v>46253</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46036</v>
+        <v>45847</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45987</v>
+        <v>45791</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 41950-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46075</v>
+        <v>46303</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46079</v>
+        <v>45987</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46079</v>
+        <v>45666</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46029</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>45905</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>45919</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45919</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>45919</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>44912</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45303</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>45063</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>46154</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>45977</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>45981</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>44973</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>44912</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>46036</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>46036</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>46075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>46079</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>46079</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>44896</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>44973</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>44937</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45260</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>46126</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44896</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>45791</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45062</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>44910</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>46275</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46275</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>46279</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>46280</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>46283</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>45791</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>46246</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>45631</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>46251</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>46253</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>45847</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>45791</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46303</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45987</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>45666</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46029</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>45905</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>45919</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45919</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>45919</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>44912</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45303</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>45063</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>46154</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>45977</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>45981</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>44973</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>44912</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>46036</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>46036</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>46075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>46079</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>46079</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>44896</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>44973</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>44937</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45260</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>46126</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44896</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>45791</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45062</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>44910</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>46275</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46275</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>46279</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>46280</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>46283</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>45791</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>46246</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>45631</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>46251</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>46253</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>45847</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>45791</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46303</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45987</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>45666</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 34591-2022</t>
+          <t>A 889-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44795</v>
+        <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -992,58 +992,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Blågrönt mannagräs</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 889-2026</t>
+          <t>A 34591-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46029</v>
+        <v>44795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,20 +1073,20 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
@@ -1097,51 +1097,51 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blågrönt mannagräs</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 889-2026 artfynd.xlsx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 889-2026 karta.png", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 889-2026 georefererad karta.tif", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 889-2026 FSC-klagomål.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 889-2026 FSC-klagomål mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 889-2026 tillsynsbegäran.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 889-2026 tillsynsbegäran mail.docx", "A 889-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
         <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1473,14 +1473,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45905</v>
+        <v>44937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45919</v>
+        <v>44912</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45919</v>
+        <v>44896</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45919</v>
+        <v>45063</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>5.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44912</v>
+        <v>44973</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>5.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45303</v>
+        <v>45905</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1857,13 +1857,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1906,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1920,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45063</v>
+        <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1936,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1979,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1993,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46154</v>
+        <v>45919</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2009,7 +2004,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>7.3</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2052,7 +2047,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2066,10 +2061,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45977</v>
+        <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2082,7 +2077,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2125,7 +2120,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2139,10 +2134,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45981</v>
+        <v>45303</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2154,8 +2149,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44973</v>
+        <v>46154</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.7</v>
+        <v>7.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44912</v>
+        <v>44973</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46036</v>
+        <v>45977</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46036</v>
+        <v>45981</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46075</v>
+        <v>46036</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46079</v>
+        <v>46036</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46079</v>
+        <v>46075</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44896</v>
+        <v>46079</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44973</v>
+        <v>46079</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2865,14 +2865,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44937</v>
+        <v>45260</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45260</v>
+        <v>45631</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
         <v>46126</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44896</v>
+        <v>45062</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
         <v>45791</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45062</v>
+        <v>44910</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44910</v>
+        <v>46275</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>46275</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46279</v>
+        <v>44896</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46280</v>
+        <v>44912</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45791</v>
+        <v>46283</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46246</v>
+        <v>45791</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45631</v>
+        <v>46246</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3967,7 +3967,7 @@
         <v>46251</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>46253</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>45847</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>45791</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46303</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45987</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>45666</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 34591-2022</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44795</v>
+        <v>46075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1113,42 +1113,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Blågrönt mannagräs</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46075</v>
+        <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1202,10 +1202,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1218,42 +1218,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="I8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1323,42 +1323,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 34591-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46080</v>
+        <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,20 +1388,20 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1428,42 +1428,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blågrönt mannagräs</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1473,14 +1473,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44937</v>
+        <v>45791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44912</v>
+        <v>45905</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44896</v>
+        <v>46036</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>7.5</v>
+        <v>2.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45063</v>
+        <v>46036</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.8</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44973</v>
+        <v>45919</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.7</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45905</v>
+        <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1918,7 +1918,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45919</v>
+        <v>45303</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2003,8 +2003,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2052,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2066,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45919</v>
+        <v>46075</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2082,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2125,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2139,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45303</v>
+        <v>46079</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2149,13 +2154,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 11000-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46154</v>
+        <v>46079</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.3</v>
+        <v>2.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44973</v>
+        <v>45666</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45977</v>
+        <v>46126</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45981</v>
+        <v>45977</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46036</v>
+        <v>45981</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46036</v>
+        <v>44912</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46075</v>
+        <v>45063</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46079</v>
+        <v>46154</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>7.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46079</v>
+        <v>44973</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45260</v>
+        <v>44912</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45631</v>
+        <v>44896</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46126</v>
+        <v>45791</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>45062</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45791</v>
+        <v>44910</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44910</v>
+        <v>44973</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3310,7 +3310,7 @@
         <v>46275</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3383,7 +3383,7 @@
         <v>46275</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3456,7 +3456,7 @@
         <v>46279</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44896</v>
+        <v>46280</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44912</v>
+        <v>46283</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3668,14 +3668,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46280</v>
+        <v>44937</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46283</v>
+        <v>45260</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         <v>45791</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>46246</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46251</v>
+        <v>44896</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>7.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45847</v>
+        <v>46253</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45791</v>
+        <v>45847</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4259,7 +4259,7 @@
         <v>46303</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45987</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45666</v>
+        <v>45631</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 34591-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46080</v>
+        <v>44795</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,20 +1283,20 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -1307,10 +1307,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1323,42 +1323,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blågrönt mannagräs</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 34591-2022</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44795</v>
+        <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,19 +1388,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1428,35 +1428,35 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Blågrönt mannagräs</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
         <v>45791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45905</v>
+        <v>44937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46036</v>
+        <v>45905</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46036</v>
+        <v>45919</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1772,7 +1772,7 @@
         <v>45919</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45919</v>
+        <v>44912</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1918,7 +1918,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45303</v>
+        <v>45666</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2003,13 +2003,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2052,7 +2047,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2066,10 +2061,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46075</v>
+        <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2082,7 +2077,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2125,7 +2120,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2139,10 +2134,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46079</v>
+        <v>45303</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2154,8 +2149,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11000-2026</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46079</v>
+        <v>45063</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45666</v>
+        <v>46036</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46126</v>
+        <v>46036</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2434,7 +2434,7 @@
         <v>45977</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45981</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44912</v>
+        <v>44973</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>5.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45063</v>
+        <v>46075</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46154</v>
+        <v>46126</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.3</v>
+        <v>4.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2799,7 +2799,7 @@
         <v>44973</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44912</v>
+        <v>46154</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>7.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44896</v>
+        <v>45260</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45791</v>
+        <v>45631</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>45062</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44910</v>
+        <v>45791</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44973</v>
+        <v>44910</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3310,7 +3310,7 @@
         <v>46275</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3383,7 +3383,7 @@
         <v>46275</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3456,7 +3456,7 @@
         <v>46279</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46280</v>
+        <v>44896</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46283</v>
+        <v>44912</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3668,14 +3668,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44937</v>
+        <v>46280</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45260</v>
+        <v>46283</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         <v>45791</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>46246</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44896</v>
+        <v>46251</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7.7</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46253</v>
+        <v>45847</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 41950-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45847</v>
+        <v>46303</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 41950-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46303</v>
+        <v>45987</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 41052-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45987</v>
+        <v>46300</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45631</v>
+        <v>46079</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 34591-2022</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44795</v>
+        <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,19 +1283,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1307,10 +1307,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1323,42 +1323,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blågrönt mannagräs</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 34591-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46080</v>
+        <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,20 +1388,20 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1428,42 +1428,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blågrönt mannagräs</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45791</v>
+        <v>44896</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44937</v>
+        <v>44973</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>3.1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45905</v>
+        <v>45666</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1692,14 +1692,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45919</v>
+        <v>44937</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45919</v>
+        <v>45260</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44912</v>
+        <v>45905</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45919</v>
+        <v>44896</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45666</v>
+        <v>45919</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44896</v>
+        <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.5</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2120,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45303</v>
+        <v>45919</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2149,13 +2149,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2193,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2212,10 +2207,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45063</v>
+        <v>45303</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2227,8 +2222,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46036</v>
+        <v>45977</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46036</v>
+        <v>45981</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45977</v>
+        <v>46154</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45981</v>
+        <v>45631</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44973</v>
+        <v>46036</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.7</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46075</v>
+        <v>46036</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46126</v>
+        <v>46075</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44973</v>
+        <v>45791</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 41052-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46154</v>
+        <v>46300</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>7.3</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45260</v>
+        <v>46126</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>4.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45631</v>
+        <v>46079</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45062</v>
+        <v>46275</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45791</v>
+        <v>46275</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44910</v>
+        <v>45791</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46275</v>
+        <v>45062</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46275</v>
+        <v>44910</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3456,7 +3456,7 @@
         <v>46279</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44896</v>
+        <v>46280</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44912</v>
+        <v>46283</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46280</v>
+        <v>45791</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46283</v>
+        <v>46246</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45791</v>
+        <v>46251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.6</v>
+        <v>7.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46246</v>
+        <v>44912</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7.7</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46253</v>
+        <v>45063</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4113,7 +4113,7 @@
         <v>45847</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>46303</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45987</v>
+        <v>44973</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.7</v>
+        <v>5.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 41052-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46300</v>
+        <v>45987</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46079</v>
+        <v>44912</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44896</v>
+        <v>45905</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44973</v>
+        <v>45919</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45666</v>
+        <v>45919</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1692,14 +1692,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44937</v>
+        <v>45919</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45260</v>
+        <v>45303</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1784,8 +1784,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1833,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1847,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45905</v>
+        <v>44896</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1863,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1906,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1915,10 +1920,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44896</v>
+        <v>44912</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1931,7 +1936,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.5</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1979,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1984,14 +1989,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45919</v>
+        <v>44937</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2004,7 +2009,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2052,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2066,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45919</v>
+        <v>45977</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2082,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2125,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2139,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45919</v>
+        <v>45981</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2150,7 +2155,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2193,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2207,10 +2212,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45303</v>
+        <v>45062</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2222,13 +2227,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45977</v>
+        <v>45791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45981</v>
+        <v>44910</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46154</v>
+        <v>46279</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7.3</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45631</v>
+        <v>45791</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46036</v>
+        <v>46280</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46036</v>
+        <v>46283</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46075</v>
+        <v>46036</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45791</v>
+        <v>46036</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 41052-2026</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46300</v>
+        <v>45791</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46126</v>
+        <v>46246</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46079</v>
+        <v>46075</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46275</v>
+        <v>46251</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>7.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46275</v>
+        <v>46253</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45791</v>
+        <v>45666</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45062</v>
+        <v>45847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 41950-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44910</v>
+        <v>46303</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46279</v>
+        <v>46126</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46280</v>
+        <v>44912</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46283</v>
+        <v>44896</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>7.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 41052-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45791</v>
+        <v>46300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46246</v>
+        <v>46079</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46251</v>
+        <v>46275</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>7.7</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44912</v>
+        <v>46275</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46253</v>
+        <v>45987</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4040,7 +4040,7 @@
         <v>45063</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45847</v>
+        <v>46154</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>7.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 41950-2026</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46303</v>
+        <v>44973</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4259,7 +4259,7 @@
         <v>44973</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45987</v>
+        <v>45260</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44912</v>
+        <v>45631</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>45905</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>45919</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45919</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>45919</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45303</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>44896</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>44912</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>44937</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>45977</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>45981</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>45062</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>44910</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>46279</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45791</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>46280</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>46283</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>46036</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>46036</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>45791</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>46246</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>46075</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>46251</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>46253</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45666</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>46303</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46126</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44912</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44896</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>46300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>46079</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>46275</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>46275</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45987</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>45063</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>46154</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44973</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>44973</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45260</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>45631</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44795</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>45905</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>45919</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45919</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>45919</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45303</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>44896</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>44912</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>44937</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>45977</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>45981</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>45062</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>44910</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>46279</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45791</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>46280</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>46283</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>46036</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>46036</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>45791</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>46246</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>46075</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>46251</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>46253</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45666</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>46303</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46126</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44912</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44896</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>46300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>46079</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>46275</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>46275</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45987</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>45063</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>46154</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44973</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>44973</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45260</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>45631</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 34591-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46075</v>
+        <v>44795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1113,42 +1113,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Blågrönt mannagräs</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46080</v>
+        <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,34 +1178,34 @@
         </is>
       </c>
       <c r="I7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="n">
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1218,42 +1218,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 11240-2026</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1323,42 +1323,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 34591-2022</t>
+          <t>A 11240-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44795</v>
+        <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,19 +1388,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1428,35 +1428,35 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Blågrönt mannagräs</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11240-2026 artfynd.xlsx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11240-2026 karta.png", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11240-2026 georefererad karta.tif", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11240-2026 FSC-klagomål.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11240-2026 FSC-klagomål mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11240-2026 tillsynsbegäran.docx", "A 11240-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11240-2026 tillsynsbegäran mail.docx", "A 11240-2026")</f>
         <v/>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
         <v>45905</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>45919</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1626,7 +1626,7 @@
         <v>45919</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1699,7 +1699,7 @@
         <v>45919</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45303</v>
+        <v>45631</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1784,13 +1784,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1833,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1847,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44896</v>
+        <v>45303</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1860,6 +1855,11 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>TJÖRN</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1906,7 +1906,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44912</v>
+        <v>45977</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1989,14 +1989,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44937</v>
+        <v>45981</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.2</v>
+        <v>3.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45977</v>
+        <v>45791</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2125,7 +2125,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2139,10 +2139,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45981</v>
+        <v>45666</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45062</v>
+        <v>46036</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45791</v>
+        <v>46036</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44910</v>
+        <v>46075</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46279</v>
+        <v>44912</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2507,7 +2507,7 @@
         <v>45791</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46280</v>
+        <v>45062</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46283</v>
+        <v>44910</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46036</v>
+        <v>45063</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>5.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46036</v>
+        <v>46280</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45791</v>
+        <v>46126</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46246</v>
+        <v>46283</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46075</v>
+        <v>44973</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>5.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46251</v>
+        <v>45791</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7.7</v>
+        <v>4.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46253</v>
+        <v>46246</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45666</v>
+        <v>44912</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45847</v>
+        <v>46154</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>7.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 41950-2026</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46303</v>
+        <v>44896</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46126</v>
+        <v>46251</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.7</v>
+        <v>7.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44912</v>
+        <v>44973</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3595,14 +3595,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44896</v>
+        <v>44937</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>7.5</v>
+        <v>0.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 41052-2026</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46300</v>
+        <v>45260</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46079</v>
+        <v>46253</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46275</v>
+        <v>44896</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46275</v>
+        <v>45847</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 41950-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45987</v>
+        <v>46303</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 41052-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45063</v>
+        <v>46300</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46154</v>
+        <v>46079</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44973</v>
+        <v>46275</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44973</v>
+        <v>46275</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45260</v>
+        <v>46279</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45631</v>
+        <v>45987</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 42462-2025</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45905</v>
+        <v>45063</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45919</v>
+        <v>44973</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1619,14 +1619,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45919</v>
+        <v>44937</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 42462-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45919</v>
+        <v>45905</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45631</v>
+        <v>45919</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45303</v>
+        <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1857,13 +1857,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1906,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1920,10 +1915,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45977</v>
+        <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1936,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1979,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1993,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45981</v>
+        <v>45303</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2008,8 +2003,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45791</v>
+        <v>44912</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2125,7 +2125,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2139,10 +2139,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45666</v>
+        <v>44896</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>7.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46036</v>
+        <v>44973</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46036</v>
+        <v>45977</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46075</v>
+        <v>45981</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44912</v>
+        <v>45791</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45791</v>
+        <v>46036</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45062</v>
+        <v>46036</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44910</v>
+        <v>45062</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45063</v>
+        <v>45791</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5.8</v>
+        <v>2.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46280</v>
+        <v>44910</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46126</v>
+        <v>46283</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46283</v>
+        <v>46075</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44973</v>
+        <v>45260</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>45791</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>46246</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44912</v>
+        <v>45631</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46154</v>
+        <v>46251</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44896</v>
+        <v>46253</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46251</v>
+        <v>45847</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44973</v>
+        <v>46126</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 41950-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3595,14 +3595,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44937</v>
+        <v>46303</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45260</v>
+        <v>44896</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46253</v>
+        <v>44912</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44896</v>
+        <v>45666</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>7.5</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 41052-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45847</v>
+        <v>46300</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 41950-2026</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46303</v>
+        <v>46079</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 41052-2026</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46300</v>
+        <v>46275</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46079</v>
+        <v>46275</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46275</v>
+        <v>45987</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46275</v>
+        <v>46154</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>7.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45987</v>
+        <v>46279</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 34591-2022</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44795</v>
+        <v>46075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1113,42 +1113,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Blågrönt mannagräs</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46075</v>
+        <v>46080</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1202,10 +1202,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1218,42 +1218,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 34591-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46080</v>
+        <v>44795</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,34 +1283,34 @@
         </is>
       </c>
       <c r="I8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="J8" t="n">
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1323,35 +1323,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blågrönt mannagräs</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45063</v>
+        <v>44973</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44973</v>
+        <v>44912</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 1103-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1619,14 +1619,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44937</v>
+        <v>45666</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1699,7 +1699,7 @@
         <v>45905</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45919</v>
+        <v>44896</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1845,7 +1845,7 @@
         <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45303</v>
+        <v>45919</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2003,13 +2003,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2052,7 +2047,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2066,10 +2061,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44912</v>
+        <v>44973</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2082,7 +2077,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2125,7 +2120,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2139,10 +2134,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44896</v>
+        <v>45303</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2154,8 +2149,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2208,14 +2208,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44973</v>
+        <v>44937</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.1</v>
+        <v>0.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45977</v>
+        <v>45260</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45981</v>
+        <v>44896</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45791</v>
+        <v>45977</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46036</v>
+        <v>45981</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46036</v>
+        <v>46154</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>7.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45062</v>
+        <v>46036</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45791</v>
+        <v>46036</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44910</v>
+        <v>46075</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46283</v>
+        <v>45631</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46075</v>
+        <v>46126</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45260</v>
+        <v>45791</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 23294-2025</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45791</v>
+        <v>45062</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33335-2026</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46246</v>
+        <v>44910</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45631</v>
+        <v>45791</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46251</v>
+        <v>46283</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>7.7</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 23294-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46253</v>
+        <v>45791</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 33335-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45847</v>
+        <v>46246</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46126</v>
+        <v>46251</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.7</v>
+        <v>7.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 41950-2026</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46303</v>
+        <v>46253</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44896</v>
+        <v>45847</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 41950-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44912</v>
+        <v>46303</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 1103-2025</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45666</v>
+        <v>44912</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 41052-2026</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46300</v>
+        <v>45063</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 41052-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46079</v>
+        <v>46300</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46275</v>
+        <v>46079</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4113,7 +4113,7 @@
         <v>46275</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45987</v>
+        <v>46275</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46154</v>
+        <v>45987</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7.3</v>
+        <v>2.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>

--- a/Översikt TJÖRN.xlsx
+++ b/Översikt TJÖRN.xlsx
@@ -601,7 +601,7 @@
         <v>45789</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45974</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45646</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 10354-2026</t>
+          <t>A 34591-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46075</v>
+        <v>44795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1113,42 +1113,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Blågrönt mannagräs</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11250-2026</t>
+          <t>A 10354-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46080</v>
+        <v>46075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1178,34 +1178,34 @@
         </is>
       </c>
       <c r="I7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="n">
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1218,42 +1218,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 10354-2026 artfynd.xlsx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 10354-2026 karta.png", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 10354-2026 georefererad karta.tif", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 10354-2026 FSC-klagomål.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 10354-2026 FSC-klagomål mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 10354-2026 tillsynsbegäran.docx", "A 10354-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 10354-2026 tillsynsbegäran mail.docx", "A 10354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 34591-2022</t>
+          <t>A 11250-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44795</v>
+        <v>46080</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1295,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1307,10 +1307,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1323,35 +1323,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blågrönt mannagräs</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 34591-2022 artfynd.xlsx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/artfynd/A 11250-2026 artfynd.xlsx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 34591-2022 karta.png", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor/A 11250-2026 karta.png", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 34591-2022 georefererad karta.tif", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/kartor_geotiff/A 11250-2026 georefererad karta.tif", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 34591-2022 FSC-klagomål.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomål/A 11250-2026 FSC-klagomål.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 34591-2022 FSC-klagomål mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/klagomålsmail/A 11250-2026 FSC-klagomål mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 34591-2022 tillsynsbegäran.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsyn/A 11250-2026 tillsynsbegäran.docx", "A 11250-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 34591-2022 tillsynsbegäran mail.docx", "A 34591-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1419/tillsynsmail/A 11250-2026 tillsynsbegäran mail.docx", "A 11250-2026")</f>
         <v/>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 7787-2023</t>
+          <t>A 2433-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44973</v>
+        <v>46036</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60717-2022</t>
+          <t>A 2434-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44912</v>
+        <v>46036</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1626,7 +1626,7 @@
         <v>45666</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>45905</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 59192-2022</t>
+          <t>A 45167-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44896</v>
+        <v>45919</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 45167-2025</t>
+          <t>A 45088-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1845,7 +1845,7 @@
         <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1901,7 +1901,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 45088-2025</t>
+          <t>A 45158-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1918,7 +1918,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 45158-2025</t>
+          <t>A 1379-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45919</v>
+        <v>45303</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2003,8 +2003,13 @@
           <t>TJÖRN</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2052,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 7791-2023</t>
+          <t>A 10340-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2066,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44973</v>
+        <v>46075</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2082,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2125,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1379-2024</t>
+          <t>A 60718-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2139,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45303</v>
+        <v>44912</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2149,13 +2154,8 @@
           <t>TJÖRN</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 1486-2023</t>
+          <t>A 57000-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2208,14 +2208,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44937</v>
+        <v>45977</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 60793-2023</t>
+          <t>A 57655-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45260</v>
+        <v>45981</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 57410-2022</t>
+          <t>A 21379-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44896</v>
+        <v>45063</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 57000-2025</t>
+          <t>A 7787-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45977</v>
+        <v>44973</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>5.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 57655-2025</t>
+          <t>A 18290-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45981</v>
+        <v>46126</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 22419-2026</t>
+          <t>A 60717-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46154</v>
+        <v>44912</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>7.3</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 2433-2026</t>
+          <t>A 59192-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46036</v>
+        <v>44896</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 2434-2026</t>
+          <t>A 7791-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46036</v>
+        <v>44973</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 10340-2026</t>
+          <t>A 1486-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2792,14 +2792,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46075</v>
+        <v>44937</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 57955-2024</t>
+          <t>A 22419-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45631</v>
+        <v>46154</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>7.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 18290-2026</t>
+          <t>A 60793-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46126</v>
+        <v>45260</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 23295-2025</t>
+          <t>A 57410-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45791</v>
+        <v>44896</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>7.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21141-2023</t>
+          <t>A 23295-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45062</v>
+        <v>45791</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60392-2022</t>
+          <t>A 21141-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44910</v>
+        <v>45062</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23301-2025</t>
+          <t>A 60392-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45791</v>
+        <v>44910</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 38523-2026</t>
+          <t>A 57955-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46283</v>
+        <v>45631</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>45791</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46246</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33757-2026</t>
+          <t>A 23301-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46251</v>
+        <v>45791</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7.7</v>
+        <v>2.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 34198-2026</t>
+          <t>A 33757-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>7.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34508-2025</t>
+          <t>A 34198-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45847</v>
+        <v>46253</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 41950-2026</t>
+          <t>A 34508-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46303</v>
+        <v>45847</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60718-2022</t>
+          <t>A 41950-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44912</v>
+        <v>46303</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 21379-2023</t>
+          <t>A 41052-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45063</v>
+        <v>46300</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 41052-2026</t>
+          <t>A 11042-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46300</v>
+        <v>46079</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11042-2026</t>
+          <t>A 37468-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46079</v>
+        <v>46275</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 37468-2026</t>
+          <t>A 37470-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4113,7 +4113,7 @@
         <v>46275</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 37470-2026</t>
+          <t>A 37741-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 59011-2025</t>
+          <t>A 37962-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45987</v>
+        <v>46280</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 37741-2026</t>
+          <t>A 38523-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37962-2026</t>
+          <t>A 59011-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46280</v>
+        <v>45987</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
